--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Llama-3.1-8B-Instruct/simple/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Llama-3.1-8B-Instruct/simple/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>168</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>56</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="G2">
-        <v>414</v>
+        <v>160</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>9</v>
+        <v>173</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="G3">
-        <v>410</v>
+        <v>180</v>
       </c>
       <c r="H3">
         <v>426</v>

--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Llama-3.1-8B-Instruct/simple/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Llama-3.1-8B-Instruct/simple/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>168</v>
+        <v>132</v>
       </c>
       <c r="D2">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E2">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="G2">
-        <v>160</v>
+        <v>206</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="D3">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E3">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G3">
-        <v>180</v>
+        <v>212</v>
       </c>
       <c r="H3">
         <v>426</v>
